--- a/results/andar_할인율모니터링_20260917.xlsx
+++ b/results/andar_할인율모니터링_20260917.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H176"/>
+  <dimension ref="A1:H177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,7 +613,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3,574</t>
+          <t>3,577</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3,574</t>
+          <t>3,577</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>457</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1255,42 +1255,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17414&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EPTBG-01</t>
+          <t>EPTSC-04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>에어플라이 프리런 러닝 벨트</t>
+          <t>[3 SET] 필라테스 삭스</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>41,700</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>27,000</t>
+          <t>30,900</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>423</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EPTSC-04</t>
+          <t>EPTSC-05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>423</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EPTSC-05</t>
+          <t>EPTSC-06</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>423</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1381,42 +1381,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17414&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EPTSC-06</t>
+          <t>EPTBG-01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>[3 SET] 필라테스 삭스</t>
+          <t>에어플라이 프리런 러닝 벨트</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>41,700</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>30,900</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>69</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1507,27 +1507,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9023&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16031&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EMTBG-03</t>
+          <t>EOTGL-02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>숄더 앤 크로스백</t>
+          <t>히트 런 글러브</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1537,39 +1537,39 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>8,147</t>
+          <t>217</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13409&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9023&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EOTBG-10</t>
+          <t>EMTBG-03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>에어플라이 투웨이 프리런 백 3.0</t>
+          <t>숄더 앤 크로스백</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1579,39 +1579,39 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1,146</t>
+          <t>8,149</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16031&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13409&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EOTGL-02</t>
+          <t>EOTBG-10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>히트 런 글러브</t>
+          <t>에어플라이 투웨이 프리런 백 3.0</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1621,133 +1621,133 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>1,146</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8838&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15350&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EMTSV-03</t>
+          <t>EOTSC-09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[1&amp;1] 서포트 무릎 보호대</t>
+          <t>[1&amp;1] 컴프레션 러닝 니삭스</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2,019</t>
+          <t>695</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15350&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8838&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EOTSC-09</t>
+          <t>EMTSV-03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[1&amp;1] 컴프레션 러닝 니삭스</t>
+          <t>[1&amp;1] 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>2,019</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13838&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15403&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EOTFB-01</t>
+          <t>EOTBG-21</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>에어쿨링 와이드 헤드밴드</t>
+          <t>데일리 라운드백</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>75,000</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2,443</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1759,37 +1759,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15403&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16868&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EOTBG-21</t>
+          <t>EPTBG-03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>데일리 라운드백</t>
+          <t>컴팩트 포켓 크로스백</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>75,000</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>138</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1,414</t>
+          <t>1,415</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1843,37 +1843,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16868&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13838&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EPTBG-03</t>
+          <t>EOTFB-01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>컴팩트 포켓 크로스백</t>
+          <t>에어쿨링 와이드 헤드밴드</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>2,446</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>433</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1927,84 +1927,84 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13215&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EMTSC-04</t>
+          <t>EOTCP-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
+          <t>올라운드 버킷햇</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>19,800</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>15,800</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3,213</t>
+          <t>363</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10478&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EMTSC-05</t>
+          <t>ENTBG-05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
+          <t>미니 숄더 앤 크로스백</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>19,800</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>15,800</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3,213</t>
+          <t>5,142</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -2095,84 +2095,84 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10478&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ENTBG-05</t>
+          <t>EMTSC-04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>미니 숄더 앤 크로스백</t>
+          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>19,800</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>15,800</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>5,142</t>
+          <t>3,215</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11456&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ENTSC-13</t>
+          <t>EMTSC-05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 퍼포먼스 삭스</t>
+          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>19,800</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>17,800</t>
+          <t>15,800</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>3,029</t>
+          <t>3,215</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ENTSC-14</t>
+          <t>ENTSC-13</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2221,37 +2221,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13215&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11456&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EOTCP-01</t>
+          <t>ENTSC-14</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>올라운드 버킷햇</t>
+          <t>[1&amp;1] 논슬립 퍼포먼스 삭스</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>17,800</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>3,029</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2263,17 +2263,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15428&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13852&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EOTBG-20</t>
+          <t>EOTET-03</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>클라우드 스트링 쇼퍼백</t>
+          <t>라이트 러닝 베스트</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2283,59 +2283,59 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13852&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17425&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EOTET-03</t>
+          <t>EPTSC-06</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>라이트 러닝 베스트</t>
+          <t>필라테스 크루 삭스</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2347,42 +2347,42 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17425&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15428&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EPTSC-06</t>
+          <t>EOTBG-20</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>필라테스 크루 삭스</t>
+          <t>클라우드 스트링 쇼퍼백</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -2515,148 +2515,148 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6952&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11027&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EJFST-02</t>
+          <t>ENTSC-08</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>릴렉스 요가링</t>
+          <t>[5 SET] 에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>85,000</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>6,597</t>
+          <t>820</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13853&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15372&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EOTBG-12</t>
+          <t>EOTBG-16</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>프리런 벨크로 러닝 벨트</t>
+          <t>폴더블 미니백 2.0</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>295</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15372&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6952&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EOTBG-16</t>
+          <t>EJFST-02</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>폴더블 미니백 2.0</t>
+          <t>릴렉스 요가링</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>6,597</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11027&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13853&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ENTSC-08</t>
+          <t>EOTBG-12</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>[5 SET] 에어컴피 크루 삭스</t>
+          <t>프리런 벨크로 러닝 벨트</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>85,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2666,44 +2666,44 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>248</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10940&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=5145&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ENTBG-03</t>
+          <t>EJPFR-04</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>데일리 스트링 쇼퍼백</t>
+          <t>릴렉스 폼롤러 Ⅱ</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2713,96 +2713,96 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>6,369</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15371&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10940&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EOTBG-15</t>
+          <t>ENTBG-03</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>폴더블 짐백 2.0</t>
+          <t>데일리 스트링 쇼퍼백</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>735</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15629&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15371&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EOTBG-23</t>
+          <t>EOTBG-15</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>안다르 실버 리유저블백 M</t>
+          <t>폴더블 짐백 2.0</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>6,500</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>6,500</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -2851,27 +2851,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16033&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13410&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EOTMK-02</t>
+          <t>EOTSC-09</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>소프텐션 넥마스크</t>
+          <t>컴프레션 러닝 니삭스</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2881,49 +2881,49 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>353</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=5145&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13408&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EJPFR-04</t>
+          <t>EOTSC-01</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>릴렉스 폼롤러 Ⅱ</t>
+          <t>프레시 필드 니삭스</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>6,369</t>
+          <t>299</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2935,27 +2935,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16032&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16844&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EOTCP-05</t>
+          <t>EPTET-02</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>히트 런 이어플랩 캡</t>
+          <t>언더웨어 세탁망</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2965,39 +2965,39 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13410&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16033&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EOTSC-09</t>
+          <t>EOTMK-02</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>컴프레션 러닝 니삭스</t>
+          <t>소프텐션 넥마스크</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3007,249 +3007,249 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>157</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13604&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16032&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EOTSV-01</t>
+          <t>EOTCP-05</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>[1&amp;1] 하이 서포트 무릎 보호대</t>
+          <t>히트 런 이어플랩 캡</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11962&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13604&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ENTMT-01</t>
+          <t>EOTSV-01</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>레스트 인 마블 요가매트 (4mm)</t>
+          <t>[1&amp;1] 하이 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>710</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16844&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15370&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EPTET-02</t>
+          <t>EOTBG-14</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>언더웨어 세탁망</t>
+          <t>폴더블 캐리백 2.0</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13408&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11962&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EOTSC-01</t>
+          <t>ENTMT-01</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>프레시 필드 니삭스</t>
+          <t>레스트 인 마블 요가매트 (4mm)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>269</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15370&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15408&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EOTBG-14</t>
+          <t>EOTSC-14</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>폴더블 캐리백 2.0</t>
+          <t>맨즈 논슬립 풀 토삭스</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17423&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14085&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EPTSC-04</t>
+          <t>EOTSV-04</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>필라테스 토삭스</t>
+          <t>프리런 라이트 러닝 밴드</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3259,39 +3259,39 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>129</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15408&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17423&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EOTSC-14</t>
+          <t>EPTSC-04</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>맨즈 논슬립 풀 토삭스</t>
+          <t>필라테스 토삭스</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>104</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -3439,37 +3439,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6660&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15385&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EKPMT-03</t>
+          <t>EOTSC-16</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>릴렉스 논슬립 요가 타월</t>
+          <t>[1&amp;1] 논슬립 스킨 토삭스</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>35,900</t>
+          <t>25,800</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>35,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1,562</t>
+          <t>526</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EOTSC-16</t>
+          <t>EOTSC-17</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>526</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3523,69 +3523,69 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15385&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16660&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EOTSC-17</t>
+          <t>EOTET-03</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 스킨 토삭스</t>
+          <t>맨즈 라이트 러닝 베스트</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>25,800</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9989&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6660&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EMTET-02</t>
+          <t>EKPMT-03</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>소프트 쿠셔닝 훌라후프</t>
+          <t>릴렉스 논슬립 요가 타월</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>35,900</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>35,900</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>1,563</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -3649,79 +3649,79 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16660&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12765&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EOTET-03</t>
+          <t>ENTBG-16</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>맨즈 라이트 러닝 베스트</t>
+          <t>라이트 패딩 쇼퍼백</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>624</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=5837&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EJFMB-03</t>
+          <t>ENTSC-19</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>릴렉스 짐볼 65cm</t>
+          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2,118</t>
+          <t>314</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3733,42 +3733,42 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12765&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ENTBG-16</t>
+          <t>EOTSC-14</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>라이트 패딩 쇼퍼백</t>
+          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>314</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -3805,91 +3805,91 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>587</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15377&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ENTSC-19</t>
+          <t>EOTGL-04</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
+          <t>논슬립 스킨 요기 글러브</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9989&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EOTSC-14</t>
+          <t>EMTET-02</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
+          <t>소프트 쿠셔닝 훌라후프</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>637</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3901,84 +3901,84 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10953&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=5837&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ENTSC-07</t>
+          <t>EJFMB-03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>[3 SET] 에어컴피 크루 삭스</t>
+          <t>릴렉스 짐볼 65cm</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>51,000</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>2,118</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15377&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10953&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EOTGL-04</t>
+          <t>ENTSC-07</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>논슬립 스킨 요기 글러브</t>
+          <t>[3 SET] 에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>51,000</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>562</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -4069,27 +4069,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13405&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13404&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EOTSV-01</t>
+          <t>EOTGL-01</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>하이 서포트 무릎 보호대</t>
+          <t>짐 글러브 2.0</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4099,29 +4099,29 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>290</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8769&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11459&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EMTSV-02</t>
+          <t>ENTSC-14</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>서포트 발목 보호대</t>
+          <t>논슬립 퍼포먼스 니삭스</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4141,39 +4141,39 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>753</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10554&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8578&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ENTMK-01</t>
+          <t>EMTSC-01</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>UV 프로텍션 맨즈 골프 마스크</t>
+          <t>링글 크루 삭스</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1,538</t>
+          <t>1,333</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4195,27 +4195,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13404&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13407&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EOTGL-01</t>
+          <t>EOTSV-03</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>짐 글러브 2.0</t>
+          <t>서포트 허리 보호대</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4225,39 +4225,39 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>186</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11459&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10554&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ENTSC-14</t>
+          <t>ENTMK-01</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 니삭스</t>
+          <t>UV 프로텍션 맨즈 골프 마스크</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>1,538</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4279,27 +4279,27 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8578&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16847&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EMTSC-01</t>
+          <t>EPTSC-02</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>링글 크루 삭스</t>
+          <t>하이 쿠션 테이핑 러닝 삭스</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>1,333</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4321,42 +4321,42 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15719&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8769&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EOTSC-19</t>
+          <t>EMTSV-02</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>[1&amp;1] 레그 워머</t>
+          <t>서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>725</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EOTSC-20</t>
+          <t>EOTSC-19</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4405,37 +4405,37 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16847&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15719&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EPTSC-02</t>
+          <t>EOTSC-20</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>하이 쿠션 테이핑 러닝 삭스</t>
+          <t>[1&amp;1] 레그 워머</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4615,37 +4615,37 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6664&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11130&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>EKPRB-04</t>
+          <t>ENTSV-01</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>릴렉스 3레벨 스트레칭 롱밴드</t>
+          <t>[1&amp;1] 3D 쿨링 팔토시</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>34,900</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>34,900</t>
+          <t>25,900</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>558</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4657,69 +4657,69 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6828&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6664&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>EKPET-01</t>
+          <t>EKPRB-04</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>[1&amp;1] 릴렉스 소프트 웨이트바 1kg</t>
+          <t>릴렉스 3레벨 스트레칭 롱밴드</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>41,800</t>
+          <t>34,900</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>35,600</t>
+          <t>34,900</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>470</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6661&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17424&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EKPMB-01</t>
+          <t>EPTSC-05</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>릴렉스 웨이트볼 0.5kg</t>
+          <t>필라테스 앵클 삭스</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4729,29 +4729,29 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16637&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6661&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>EPTFB-02</t>
+          <t>EKPMB-01</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>퍼포먼스 심리스 손목밴드</t>
+          <t>릴렉스 웨이트볼 0.5kg</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4771,39 +4771,39 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>698</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17424&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16637&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EPTSC-05</t>
+          <t>EPTFB-02</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>필라테스 앵클 삭스</t>
+          <t>퍼포먼스 심리스 손목밴드</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4813,39 +4813,39 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>284</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15375&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13851&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>EOTSC-16</t>
+          <t>EOTCP-03</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>논슬립 스킨 하프 토삭스</t>
+          <t>쿨 라운드 볼캡</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4855,81 +4855,81 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13407&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6828&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>EOTSV-03</t>
+          <t>EKPET-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>서포트 허리 보호대</t>
+          <t>[1&amp;1] 릴렉스 소프트 웨이트바 1kg</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>41,800</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>35,600</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>598</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11039&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16650&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ENTFB-01</t>
+          <t>EPTCP-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>에어쿨링 라인 스크런치</t>
+          <t>시그니처 로고 나일론 볼캡</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>1,094</t>
+          <t>1,097</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4993,27 +4993,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13851&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15375&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EOTCP-03</t>
+          <t>EOTSC-16</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>쿨 라운드 볼캡</t>
+          <t>논슬립 스킨 하프 토삭스</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5023,81 +5023,81 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12480&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8837&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ENTSC-24</t>
+          <t>EMTSV-02</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>웜 슬릿 레그 워머</t>
+          <t>[1&amp;1] 서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>725</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16650&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8727&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>EPTCP-02</t>
+          <t>EMTSC-04</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>시그니처 로고 나일론 볼캡</t>
+          <t>논슬립 서포트 하프 토삭스 (HOLE)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>646</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5119,27 +5119,27 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14562&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11039&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EOTBG-11</t>
+          <t>ENTFB-01</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>메쉬 파우치</t>
+          <t>에어쿨링 라인 스크런치</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5149,12 +5149,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>776</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -5413,42 +5413,42 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8837&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10657&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EMTSV-02</t>
+          <t>EMTSC-17</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>[1&amp;1] 서포트 발목 보호대</t>
+          <t>[3 SET] 맨즈 클래식 삭스</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>20,700</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -5497,27 +5497,27 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12793&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15733&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ENTMU-01</t>
+          <t>EOTSC-19</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>소프트 니트 머플러</t>
+          <t>레그 숏 워머</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5539,27 +5539,27 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15733&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12793&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EOTSC-19</t>
+          <t>ENTMU-01</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>레그 숏 워머</t>
+          <t>소프트 니트 머플러</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>472</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5581,69 +5581,69 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10657&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13854&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EMTSC-17</t>
+          <t>EOTSC-06</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>[3 SET] 맨즈 클래식 삭스</t>
+          <t>서포트 쿠션 러닝 삭스</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>20,700</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>770</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13854&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15629&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EOTSC-06</t>
+          <t>EOTBG-23</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>서포트 쿠션 러닝 삭스</t>
+          <t>안다르 실버 리유저블백 M</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>6,500</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>6,500</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5653,39 +5653,39 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>379</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6665&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15376&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EKPRB-05</t>
+          <t>EOTSC-17</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>릴렉스 4레벨 힙 밴드</t>
+          <t>논슬립 스킨 토삭스</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>21,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>21,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5695,39 +5695,39 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15376&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6665&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EOTSC-17</t>
+          <t>EKPRB-05</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>논슬립 스킨 토삭스</t>
+          <t>릴렉스 4레벨 힙 밴드</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>21,900</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>21,900</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5737,39 +5737,39 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>527</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16036&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14562&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EOTCP-06</t>
+          <t>EOTBG-11</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>소프트 니트 버킷햇</t>
+          <t>메쉬 파우치</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5779,54 +5779,54 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>193</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8836&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16036&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EMTSV-01</t>
+          <t>EOTCP-06</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>[1&amp;1] 서포트 팔꿈치 보호대</t>
+          <t>소프트 니트 버킷햇</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -5917,27 +5917,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13806&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13805&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>EOTSC-05</t>
+          <t>EOTSC-04</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>올데이 수피마 앵클 삭스</t>
+          <t>올데이 수피마 스니커즈 삭스</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5947,39 +5947,39 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>433</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8728&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13806&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>EMTSC-05</t>
+          <t>EOTSC-05</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>논슬립 서포트 하프 토삭스 (SOLID)</t>
+          <t>올데이 수피마 앵클 삭스</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5989,39 +5989,39 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>479</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6662&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8728&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>EKPMB-02</t>
+          <t>EMTSC-05</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>릴렉스 미니 짐볼</t>
+          <t>논슬립 서포트 하프 토삭스 (SOLID)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6031,39 +6031,39 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>1,234</t>
+          <t>569</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13805&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12783&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>EOTSC-04</t>
+          <t>ENTSC-26</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>올데이 수피마 스니커즈 삭스</t>
+          <t>니트 기모 오버 니삭스</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>354</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6085,27 +6085,27 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13566&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6662&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>EOTSC-10</t>
+          <t>EKPMB-02</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>시그니처 로고 맨즈 크루 삭스</t>
+          <t>릴렉스 미니 짐볼</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6115,76 +6115,76 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>1,234</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12783&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8836&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ENTSC-26</t>
+          <t>EMTSV-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>니트 기모 오버 니삭스</t>
+          <t>[1&amp;1] 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>593</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15867&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12794&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>EOTSC-18</t>
+          <t>ENTFB-05</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>[1&amp;1] 올데이 기모 삭스</t>
+          <t>소프트 니트 헤드밴드</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -6194,12 +6194,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>913</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6211,27 +6211,27 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12794&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13566&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ENTFB-05</t>
+          <t>EOTSC-10</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>소프트 니트 헤드밴드</t>
+          <t>시그니처 로고 맨즈 크루 삭스</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6253,37 +6253,37 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15732&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15867&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>EOTSC-11</t>
+          <t>EOTSC-18</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>웜 레그 롱 워머</t>
+          <t>[1&amp;1] 올데이 기모 삭스</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>225</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6337,27 +6337,27 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14084&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12480&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>EOTET-01</t>
+          <t>ENTSC-24</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>소프트 뱀부 롱 타월</t>
+          <t>웜 슬릿 레그 워머</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6367,39 +6367,39 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14085&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13405&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>EOTSV-04</t>
+          <t>EOTSV-01</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>프리런 라이트 러닝 밴드</t>
+          <t>하이 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6409,19 +6409,19 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>710</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11130&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11061&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6431,22 +6431,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>[1&amp;1] 3D 쿨링 팔토시</t>
+          <t>3D 쿨링 팔토시</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>25,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -6463,27 +6463,27 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11061&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11457&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ENTSV-01</t>
+          <t>ENTSC-12</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>3D 쿨링 팔토시</t>
+          <t>논슬립 퍼포먼스 토삭스</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>4,136</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6505,37 +6505,37 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11457&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9612&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ENTSC-12</t>
+          <t>EMTSC-28</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 토삭스</t>
+          <t>[1&amp;1] 리브드 셔링 루즈 삭스</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>4,136</t>
+          <t>395</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6547,69 +6547,69 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9612&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15732&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>EMTSC-28</t>
+          <t>EOTSC-11</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>[1&amp;1] 리브드 셔링 루즈 삭스</t>
+          <t>웜 레그 롱 워머</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14561&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14084&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>EOTBG-05</t>
+          <t>EOTET-01</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>메쉬 포켓 비치백</t>
+          <t>소프트 뱀부 롱 타월</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>240</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6631,27 +6631,27 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16035&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14561&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>EOTSC-12</t>
+          <t>EOTBG-05</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>소프트 니트 기모 니삭스</t>
+          <t>메쉬 포켓 비치백</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -6661,81 +6661,81 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8770&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17857&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>EMTSV-03</t>
+          <t>EPTSC-03</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>서포트 무릎 보호대</t>
+          <t>[1&amp;1] 데일리 루즈 삭스</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>18,900</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2,019</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12795&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8770&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ENTCP-05</t>
+          <t>EMTSV-03</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>소프트 니트 비니</t>
+          <t>서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6745,39 +6745,39 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>2,019</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9993&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12795&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>EMTSC-29</t>
+          <t>ENTCP-05</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>니트 루즈 삭스</t>
+          <t>소프트 니트 비니</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6787,39 +6787,39 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>363</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8727&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9993&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>EMTSC-04</t>
+          <t>EMTSC-29</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>논슬립 서포트 하프 토삭스 (HOLE)</t>
+          <t>니트 루즈 삭스</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>513</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6841,37 +6841,37 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17857&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12778&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>EPTSC-03</t>
+          <t>ENTBG-14</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>[1&amp;1] 데일리 루즈 삭스</t>
+          <t>웨이브 패딩 파우치</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>18,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>195</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6883,27 +6883,27 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12778&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11725&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ENTBG-14</t>
+          <t>ENTFB-04</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>웨이브 패딩 파우치</t>
+          <t>더블 링글 손목밴드</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -6913,39 +6913,39 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>435</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11725&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16035&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ENTFB-04</t>
+          <t>EOTSC-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>더블 링글 손목밴드</t>
+          <t>소프트 니트 기모 니삭스</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -7009,27 +7009,27 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11110&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17842&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ENTCP-01</t>
+          <t>EPTSC-03</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>와이드 셰이드 버킷햇</t>
+          <t>데일리 루즈 삭스</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7039,39 +7039,39 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17440&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11110&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EPTET-03</t>
+          <t>ENTCP-01</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>안다르 3단 양우산</t>
+          <t>와이드 셰이드 버킷햇</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -7081,39 +7081,39 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>686</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17386&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17440&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EPTSC-07</t>
+          <t>EPTET-03</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>맨즈 필라테스 앵클 삭스</t>
+          <t>안다르 3단 양우산</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -7123,39 +7123,39 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>38</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.4</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15144&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17386&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EOTBO-01</t>
+          <t>EPTSC-07</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>액티브 스포츠 보틀 (650ml)</t>
+          <t>맨즈 필라테스 앵클 삭스</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7165,39 +7165,39 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17842&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15144&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EPTSC-03</t>
+          <t>EOTBO-01</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>데일리 루즈 삭스</t>
+          <t>액티브 스포츠 보틀 (650ml)</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>290</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -7261,27 +7261,27 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13831&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=5144&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EOTCP-02</t>
+          <t>EJPMS-05</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>데님 로고 볼캡</t>
+          <t>릴렉스 마사지 스틱 Ⅱ</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10,380</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -7303,111 +7303,111 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10939&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13831&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ENTSC-07</t>
+          <t>EOTCP-02</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>에어컴피 크루 삭스</t>
+          <t>데님 로고 볼캡</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12792&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10939&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ENTGL-05</t>
+          <t>ENTSC-07</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>니트 글러브</t>
+          <t>에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>23,900</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>23,900</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>562</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11963&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12792&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ENTSC-19</t>
+          <t>ENTGL-05</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>맨즈 논슬립 하프 토삭스</t>
+          <t>니트 글러브</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>23,900</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>23,900</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>373</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7429,27 +7429,27 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17415&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11963&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>EPTSC-01</t>
+          <t>ENTSC-19</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>쿨 메쉬 서포트 러닝 삭스</t>
+          <t>맨즈 논슬립 하프 토삭스</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7471,17 +7471,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9599&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17415&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>EMTSC-28</t>
+          <t>EPTSC-01</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>리브드 셔링 루즈 삭스</t>
+          <t>쿨 메쉬 서포트 러닝 삭스</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -7513,27 +7513,27 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17387&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9599&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>EPTSC-08</t>
+          <t>EMTSC-28</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>맨즈 필라테스 크루 삭스</t>
+          <t>리브드 셔링 루즈 삭스</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7543,39 +7543,39 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>395</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16640&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17387&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>EPTBG-05</t>
+          <t>EPTSC-08</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>안다르 시그니처 로고 에코백</t>
+          <t>맨즈 필라테스 크루 삭스</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -7585,39 +7585,39 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15865&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16640&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>EOTSC-18</t>
+          <t>EPTBG-05</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>올데이 기모 삭스</t>
+          <t>안다르 시그니처 로고 에코백</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -7627,39 +7627,39 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.3</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15151&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15865&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>EOTBG-22</t>
+          <t>EOTSC-18</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>투포켓 로고 캔버스백</t>
+          <t>올데이 기모 삭스</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -7669,91 +7669,91 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>225</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13605&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15151&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>EOTSV-02</t>
+          <t>EOTBG-22</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>[1&amp;1] 하이 서포트 팔꿈치 보호대</t>
+          <t>투포켓 로고 캔버스백</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>38</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11092&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13605&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ENTSC-05</t>
+          <t>EOTSV-02</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>에어프레시 크루 삭스</t>
+          <t>[1&amp;1] 하이 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>156</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -7765,40 +7765,82 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=11092&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>ENTSC-05</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>에어프레시 크루 삭스</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>17,000</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
           <t>https://andar.co.kr/product/detail.html?product_no=6666&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B177" t="inlineStr">
         <is>
           <t>EKPET-01</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
+      <c r="C177" t="inlineStr">
         <is>
           <t>릴렉스 소프트 웨이트바 1kg</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
+      <c r="D177" t="inlineStr">
         <is>
           <t>20,900</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
+      <c r="E177" t="inlineStr">
         <is>
           <t>20,900</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
+      <c r="H177" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
